--- a/brigadas_template.xlsx
+++ b/brigadas_template.xlsx
@@ -672,6 +672,13 @@
       <c r="H5" t="n">
         <v>1</v>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>General|https://drive.google.com/drive/folders/1Jn3Zg-V2umhoep5QKUiO3SPoiXm3VZUQ?usp=sharing
+Identificacion|https://drive.google.com/drive/folders/1RLG5BTS_p_zFKUS3ye8ZhytzGvplL_QW?usp=drive_link
+Material complementario|https://drive.google.com/drive/folders/17g4oBDcsGCvQXkPuojPtZvTVVnx-7ECp?usp=drive_link</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -789,7 +796,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:K8"/>
-  <dataValidations count="7">
+  <dataValidations count="9">
     <dataValidation sqref="F2:F1000 G2:G1000 M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
@@ -800,6 +807,12 @@
       <formula1>"SI,NO"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F1000 G2:G1000 M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"SI,NO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1000 G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"SI,NO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1000 G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F1000 G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
@@ -6410,7 +6423,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O500"/>
-  <dataValidations count="56">
+  <dataValidations count="72">
     <dataValidation sqref="F2:F1000 G2:G1000 M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
@@ -6579,6 +6592,54 @@
     <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
       <formula1>"x,X,SI"</formula1>
     </dataValidation>
+    <dataValidation sqref="F2:F1000 G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"SI,NO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"x,X,SI"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"x,X,SI"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"x,X,SI"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"x,X,SI"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"x,X,SI"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"x,X,SI"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"x,X,SI"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1000 G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"SI,NO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"x,X,SI"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"x,X,SI"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"x,X,SI"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"x,X,SI"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"x,X,SI"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"x,X,SI"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"x,X,SI"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9677,7 +9738,13 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:N500"/>
-  <dataValidations count="7">
+  <dataValidations count="9">
+    <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"Programado,Realizado,Suspendido,Reprogramado,Pendiente"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"Programado,Realizado,Suspendido,Reprogramado,Pendiente"</formula1>
+    </dataValidation>
     <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
       <formula1>"Programado,Realizado,Suspendido,Reprogramado,Pendiente"</formula1>
     </dataValidation>
@@ -12791,7 +12858,13 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:M500"/>
-  <dataValidations count="7">
+  <dataValidations count="9">
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"Borrador,Cerrado,Anulado"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"Borrador,Cerrado,Anulado"</formula1>
+    </dataValidation>
     <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
       <formula1>"Borrador,Cerrado,Anulado"</formula1>
     </dataValidation>
@@ -12881,7 +12954,13 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
-  <dataValidations count="7">
+  <dataValidations count="9">
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"P,A,Just."</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"P,A,Just."</formula1>
+    </dataValidation>
     <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
       <formula1>"P,A,Just."</formula1>
     </dataValidation>
@@ -12972,7 +13051,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G1"/>
-  <dataValidations count="14">
+  <dataValidations count="19">
     <dataValidation sqref="F2:F1000 G2:G1000 M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
@@ -13015,6 +13094,21 @@
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
       <formula1>"BUENO,MALO"</formula1>
     </dataValidation>
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"OK,NO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"BUENO,MALO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"Rescate acuatico,Buceo,K9,Mat Pel,Altura,Socorrismo,BREC"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"OK,NO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"BUENO,MALO"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16105,7 +16199,7 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L500"/>
-  <dataValidations count="11">
+  <dataValidations count="16">
     <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
       <formula1>"OK,Observado,Critico"</formula1>
     </dataValidation>
@@ -16132,6 +16226,21 @@
     </dataValidation>
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
       <formula1>"BUENO,MALO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"OK,NO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"BUENO,MALO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"OK,NO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"BUENO,MALO"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"Rescate acuatico,Buceo,K9,Mat Pel,Altura,Socorrismo,BREC"</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
       <formula1>"OK,NO"</formula1>
@@ -19273,7 +19382,19 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:T500"/>
-  <dataValidations count="14">
+  <dataValidations count="18">
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"Alta,Media,Baja"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"Pendiente,Cotizado,Solicitado,Comprado,Recibido,Cancelado"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"Alta,Media,Baja"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
+      <formula1>"Pendiente,Cotizado,Solicitado,Comprado,Recibido,Cancelado"</formula1>
+    </dataValidation>
     <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Validacion" error="Valor no permitido" type="list">
       <formula1>"Alta,Media,Baja"</formula1>
     </dataValidation>
